--- a/analyse_daten.xlsx
+++ b/analyse_daten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mirii\desktop\Masterarbeit\Thesis r codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56279605-E02E-41D7-A45A-891F8D3A41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE18BF9-C0E9-4B04-98EA-174989F5549F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11C6B6DC-7E62-4EC8-942E-825C2E542173}"/>
   </bookViews>
@@ -1488,6 +1488,8 @@
     <col min="11" max="11" width="15.7265625" customWidth="1"/>
     <col min="12" max="12" width="17.1796875" customWidth="1"/>
     <col min="13" max="13" width="16.26953125" customWidth="1"/>
+    <col min="15" max="15" width="14.36328125" customWidth="1"/>
+    <col min="16" max="16" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
